--- a/data/trans_dic/P43C-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Provincia-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57,44%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,73%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,87; 63,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,68; 77,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,14; 76,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,33; 94,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,86; 63,69</t>
+          <t>50,87; 63,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,23; 77,52</t>
+          <t>65,68; 77,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,59; 76,57</t>
+          <t>65,14; 76,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,19; 94,57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50,86; 63,69</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>66,23; 77,52</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65,59; 76,57</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,19; 94,57</t>
+          <t>82,33; 94,52</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58,59%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>54,63%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>73,81%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>58,59%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,57; 59,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,91; 76,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69,19; 77,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,23; 63,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,24; 59,35</t>
+          <t>50,57; 59,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,74; 76,7</t>
+          <t>68,91; 76,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,88; 77,52</t>
+          <t>69,19; 77,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,79; 63,38</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>50,24; 59,35</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68,74; 76,7</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>69,88; 77,52</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>53,79; 63,38</t>
+          <t>54,23; 63,29</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>56,74%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>56,63%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,52%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,4; 62,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,02; 62,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73,69; 82,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,76; 67,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,34; 62,27</t>
+          <t>51,4; 62,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,72; 62,21</t>
+          <t>51,02; 62,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,01; 83,04</t>
+          <t>73,69; 82,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57,11; 67,52</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>51,34; 62,27</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50,72; 62,21</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>74,01; 83,04</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>57,11; 67,52</t>
+          <t>56,76; 67,75</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>75,91%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>67,1%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>69,9%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,91%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,27; 61,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61,83; 72,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,27; 74,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,34; 86,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,55; 61,8</t>
+          <t>51,27; 61,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,81; 72,0</t>
+          <t>61,83; 72,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,05; 74,92</t>
+          <t>65,27; 74,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,25; 87,75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51,55; 61,8</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61,81; 72,0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>65,05; 74,92</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>67,25; 87,75</t>
+          <t>66,34; 86,96</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39,76%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>63,12%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>43,89%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>39,76%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,97; 49,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,56; 69,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,89; 50,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,44; 44,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,26; 48,78</t>
+          <t>34,97; 49,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,58; 69,89</t>
+          <t>56,56; 69,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,8; 50,39</t>
+          <t>37,89; 50,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,61; 44,93</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34,26; 48,78</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>56,58; 69,89</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>36,8; 50,39</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>34,61; 44,93</t>
+          <t>34,44; 44,47</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>54,49%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>41,18%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,56; 52,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,08; 60,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,66; 28,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,08; 46,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,34; 52,01</t>
+          <t>40,56; 52,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,84; 59,97</t>
+          <t>48,08; 60,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,37; 28,51</t>
+          <t>18,66; 28,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,37; 47,1</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>40,34; 52,01</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47,84; 59,97</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>18,37; 28,51</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>36,37; 47,1</t>
+          <t>36,08; 46,59</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>63,51%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>61,96%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,3%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,83; 67,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,17; 67,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,0; 65,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,76; 75,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,63; 67,25</t>
+          <t>59,83; 67,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,93; 67,56</t>
+          <t>60,17; 67,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,26; 65,84</t>
+          <t>58,0; 65,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,81; 76,02</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>59,63; 67,25</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>59,93; 67,56</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>58,26; 65,84</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>19,81; 76,02</t>
+          <t>21,76; 75,6</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1313,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,26 +1347,6 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>41,79%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>47,27%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>65,6%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>66,65%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>41,79%</t>
         </is>
@@ -1697,62 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,57; 51,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,06; 68,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,36; 69,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,2; 45,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,71; 51,27</t>
+          <t>43,57; 51,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,27; 68,85</t>
+          <t>62,06; 68,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,87; 69,95</t>
+          <t>63,36; 69,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,5; 45,51</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>43,71; 51,27</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>62,27; 68,85</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>62,87; 69,95</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>38,5; 45,51</t>
+          <t>38,2; 45,12</t>
         </is>
       </c>
     </row>
@@ -1769,22 +1413,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,26 +1447,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>55,97%</t>
         </is>
@@ -1837,62 +1461,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,41; 66,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,28; 65,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,03; 61,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51,98; 55,46</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,58; 66,93</t>
+          <t>63,41; 66,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,29; 65,57</t>
+          <t>62,28; 65,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>43,79; 61,47</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>51,98; 55,46</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>63,58; 66,93</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>62,29; 65,57</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>43,79; 61,47</t>
+          <t>42,03; 61,37</t>
         </is>
       </c>
     </row>
@@ -1904,17 +1508,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
@@ -1929,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1942,22 +1545,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,20 +1564,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2019,26 +1610,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -2055,10 +1626,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2073,22 +1640,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>176</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2107,26 +1674,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>323</t>
         </is>
@@ -2141,22 +1688,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>200802</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2175,26 +1722,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168954</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>146234</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>200802</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>202807</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>168954</t>
         </is>
@@ -2209,62 +1736,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>129510; 162241</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>183783; 216081</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>185082; 217245</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>153317; 176014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>129470; 162146</t>
+          <t>129510; 162241</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>185326; 216917</t>
+          <t>183783; 216081</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>186355; 217537</t>
+          <t>185082; 217245</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>151187; 176098</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>129470; 162146</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>185326; 216917</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>186355; 217537</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>151187; 176098</t>
+          <t>153317; 176014</t>
         </is>
       </c>
     </row>
@@ -2281,22 +1788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>325</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2315,26 +1822,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>325</t>
         </is>
@@ -2349,22 +1836,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271606</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379281</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>384163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>232783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2383,26 +1870,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>232783</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>271606</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>379281</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>384163</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>232783</t>
         </is>
@@ -2417,62 +1884,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>251430; 293675</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>357380; 398978</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>360140; 403533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>215453; 251450</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>249803; 295088</t>
+          <t>251430; 293675</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>356480; 397803</t>
+          <t>357380; 398978</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>363723; 403471</t>
+          <t>360140; 403533</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>213727; 251798</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>249803; 295088</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>356480; 397803</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>363723; 403471</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>213727; 251798</t>
+          <t>215453; 251450</t>
         </is>
       </c>
     </row>
@@ -2489,22 +1936,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>176</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2523,26 +1970,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>255</t>
         </is>
@@ -2557,22 +1984,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188097</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>192571</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2591,26 +2018,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>155723</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188097</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>192571</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>261239</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>155723</t>
         </is>
@@ -2625,62 +2032,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>170402; 206027</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>173489; 211570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>244374; 274985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>141377; 168752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>170178; 206412</t>
+          <t>170402; 206027</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>172462; 211536</t>
+          <t>173489; 211570</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>245418; 275363</t>
+          <t>244374; 274985</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142270; 168188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>170178; 206412</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172462; 211536</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>245418; 275363</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>142270; 168188</t>
+          <t>141377; 168752</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2084,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>214</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2731,26 +2118,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>316</t>
         </is>
@@ -2765,22 +2132,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209068</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260361</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>269888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2799,26 +2166,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290086</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>209068</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>260361</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>269888</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>290086</t>
         </is>
@@ -2833,62 +2180,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>189573; 227621</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>239894; 279424</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>251993; 288918</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>253516; 332305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>190609; 228484</t>
+          <t>189573; 227621</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>239836; 279363</t>
+          <t>239894; 279424</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>251138; 289254</t>
+          <t>251993; 288918</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>257001; 335340</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190609; 228484</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>239836; 279363</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>251138; 289254</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>257001; 335340</t>
+          <t>253516; 332305</t>
         </is>
       </c>
     </row>
@@ -2905,22 +2232,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2939,26 +2266,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>157</t>
         </is>
@@ -2973,22 +2280,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84813</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136664</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3007,26 +2314,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>59724</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>84813</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136664</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>94689</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>59724</t>
         </is>
@@ -3041,62 +2328,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>70992; 99587</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>122445; 150440</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81733; 109025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51736; 66797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69554; 99033</t>
+          <t>70992; 99587</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>122485; 151310</t>
+          <t>122445; 150440</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79398; 108711</t>
+          <t>81733; 109025</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51993; 67490</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>69554; 99033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>122485; 151310</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>79398; 108711</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>51993; 67490</t>
+          <t>51736; 66797</t>
         </is>
       </c>
     </row>
@@ -3113,22 +2380,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3147,26 +2414,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
@@ -3181,22 +2428,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127365</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152598</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62742</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3215,26 +2462,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>86104</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>127365</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>152598</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>62742</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>86104</t>
         </is>
@@ -3249,62 +2476,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>111468; 144066</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>134632; 169857</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50459; 78286</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>75442; 97405</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>110843; 142929</t>
+          <t>111468; 144066</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>133979; 167947</t>
+          <t>134632; 169857</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49682; 77114</t>
+          <t>50459; 78286</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>76048; 98465</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>110843; 142929</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>133979; 167947</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49682; 77114</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>76048; 98465</t>
+          <t>75442; 97405</t>
         </is>
       </c>
     </row>
@@ -3321,22 +2528,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3355,26 +2562,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>509</t>
         </is>
@@ -3389,22 +2576,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403613</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>438375</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>420196</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3423,26 +2610,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>337046</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>403613</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>438375</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>420196</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>337046</t>
         </is>
@@ -3457,62 +2624,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>380242; 430136</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>413906; 464898</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>393380; 445903</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>142939; 496637</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>378934; 427350</t>
+          <t>380242; 430136</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>412286; 464778</t>
+          <t>413906; 464898</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>395102; 446497</t>
+          <t>393380; 445903</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>130176; 499393</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>378934; 427350</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>412286; 464778</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>395102; 446497</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>130176; 499393</t>
+          <t>142939; 496637</t>
         </is>
       </c>
     </row>
@@ -3529,22 +2676,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>339</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>488</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3563,26 +2710,6 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>367</t>
         </is>
@@ -3597,22 +2724,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>359553</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>532324</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240870</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3631,26 +2758,6 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>240870</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>359553</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>532324</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>546503</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>240870</t>
         </is>
@@ -3665,62 +2772,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>331445; 388754</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>503596; 559634</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>519558; 573858</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>220180; 260079</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>332473; 389991</t>
+          <t>331445; 388754</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>505315; 558665</t>
+          <t>503596; 559634</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>515548; 573595</t>
+          <t>519558; 573858</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>221909; 262318</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>332473; 389991</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>505315; 558665</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>515548; 573595</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>221909; 262318</t>
+          <t>220180; 260079</t>
         </is>
       </c>
     </row>
@@ -3737,22 +2824,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3771,26 +2858,6 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2420</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2420</t>
         </is>
@@ -3805,22 +2872,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1790349</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2292976</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2242226</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571289</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3839,26 +2906,6 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1571289</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1790349</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>2292976</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2242226</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>1571289</t>
         </is>
@@ -3873,62 +2920,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2233561; 2345963</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2183875; 2297736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1180025; 1722853</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1729293; 1845045</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2239652; 2357380</t>
+          <t>2233561; 2345963</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2184223; 2299181</t>
+          <t>2183875; 2297736</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1229447; 1725596</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1729293; 1845045</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>2239652; 2357380</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2184223; 2299181</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1229447; 1725596</t>
+          <t>1180025; 1722853</t>
         </is>
       </c>
     </row>
@@ -3940,7 +2967,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3948,10 +2975,9 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P43C-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Provincia-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,87; 63,73</t>
+          <t>50,95; 64,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65,68; 77,22</t>
+          <t>66,01; 76,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,14; 76,46</t>
+          <t>65,77; 76,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,33; 94,52</t>
+          <t>84,27; 93,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,87; 63,73</t>
+          <t>50,95; 64,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,68; 77,22</t>
+          <t>66,01; 76,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,14; 76,46</t>
+          <t>65,77; 76,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,33; 94,52</t>
+          <t>84,27; 93,19</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,57; 59,06</t>
+          <t>49,79; 58,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,91; 76,93</t>
+          <t>68,92; 76,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,19; 77,53</t>
+          <t>69,51; 77,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,23; 63,29</t>
+          <t>53,25; 61,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,57; 59,06</t>
+          <t>49,79; 58,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,91; 76,93</t>
+          <t>68,92; 76,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,19; 77,53</t>
+          <t>69,51; 77,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,23; 63,29</t>
+          <t>53,25; 61,79</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,95%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,4; 62,15</t>
+          <t>51,15; 62,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,02; 62,22</t>
+          <t>50,73; 62,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,69; 82,92</t>
+          <t>74,3; 83,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,76; 67,75</t>
+          <t>57,83; 68,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,4; 62,15</t>
+          <t>51,15; 62,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,02; 62,22</t>
+          <t>50,73; 62,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,69; 82,92</t>
+          <t>74,3; 83,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,76; 67,75</t>
+          <t>57,83; 68,5</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 61,56</t>
+          <t>51,75; 62,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,83; 72,02</t>
+          <t>61,97; 71,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,27; 74,83</t>
+          <t>64,47; 74,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66,34; 86,96</t>
+          <t>59,24; 71,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 61,56</t>
+          <t>51,75; 62,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,83; 72,02</t>
+          <t>61,97; 71,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,27; 74,83</t>
+          <t>64,47; 74,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66,34; 86,96</t>
+          <t>59,24; 71,07</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,97; 49,06</t>
+          <t>34,36; 48,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,56; 69,49</t>
+          <t>56,63; 69,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,89; 50,54</t>
+          <t>37,43; 50,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,44; 44,47</t>
+          <t>34,71; 44,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,97; 49,06</t>
+          <t>34,36; 48,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,56; 69,49</t>
+          <t>56,63; 69,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,89; 50,54</t>
+          <t>37,43; 50,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,44; 44,47</t>
+          <t>34,71; 44,98</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,56; 52,43</t>
+          <t>40,16; 51,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48,08; 60,66</t>
+          <t>48,65; 59,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,66; 28,94</t>
+          <t>18,31; 28,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,59</t>
+          <t>35,96; 46,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,56; 52,43</t>
+          <t>40,16; 51,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,08; 60,66</t>
+          <t>48,65; 59,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,66; 28,94</t>
+          <t>18,31; 28,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,59</t>
+          <t>35,96; 46,55</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>73,74%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,83; 67,68</t>
+          <t>59,45; 67,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,17; 67,58</t>
+          <t>60,05; 67,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,0; 65,75</t>
+          <t>58,12; 65,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,76; 75,6</t>
+          <t>69,35; 77,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,83; 67,68</t>
+          <t>59,45; 67,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,17; 67,58</t>
+          <t>60,05; 67,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,0; 65,75</t>
+          <t>58,12; 65,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,76; 75,6</t>
+          <t>69,35; 77,0</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,57; 51,1</t>
+          <t>43,62; 50,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>62,06; 68,97</t>
+          <t>62,03; 69,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63,36; 69,98</t>
+          <t>63,2; 69,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38,2; 45,12</t>
+          <t>36,75; 43,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,57; 51,1</t>
+          <t>43,62; 50,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,06; 68,97</t>
+          <t>62,03; 69,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,36; 69,98</t>
+          <t>63,2; 69,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,2; 45,12</t>
+          <t>36,75; 43,41</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -1461,42 +1461,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63,41; 66,6</t>
+          <t>63,41; 66,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62,28; 65,52</t>
+          <t>62,12; 65,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42,03; 61,37</t>
+          <t>56,26; 59,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,41; 66,6</t>
+          <t>63,41; 66,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,28; 65,52</t>
+          <t>62,12; 65,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42,03; 61,37</t>
+          <t>56,26; 59,78</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182455</t>
         </is>
       </c>
     </row>
@@ -1736,42 +1736,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>129510; 162241</t>
+          <t>129707; 163697</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>183783; 216081</t>
+          <t>184720; 215241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>185082; 217245</t>
+          <t>186867; 217120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153317; 176014</t>
+          <t>171699; 189880</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>129510; 162241</t>
+          <t>129707; 163697</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>183783; 216081</t>
+          <t>184720; 215241</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>185082; 217245</t>
+          <t>186867; 217120</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>153317; 176014</t>
+          <t>171699; 189880</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
     </row>
@@ -1884,42 +1884,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>251430; 293675</t>
+          <t>247562; 292688</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>357380; 398978</t>
+          <t>357418; 399267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>360140; 403533</t>
+          <t>361768; 404177</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215453; 251450</t>
+          <t>223941; 259836</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>251430; 293675</t>
+          <t>247562; 292688</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>357380; 398978</t>
+          <t>357418; 399267</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>360140; 403533</t>
+          <t>361768; 404177</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>215453; 251450</t>
+          <t>223941; 259836</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
     </row>
@@ -2032,42 +2032,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>170402; 206027</t>
+          <t>169567; 206961</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>173489; 211570</t>
+          <t>172502; 213104</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>244374; 274985</t>
+          <t>246399; 275448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141377; 168752</t>
+          <t>147483; 174670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>170402; 206027</t>
+          <t>169567; 206961</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>173489; 211570</t>
+          <t>172502; 213104</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>244374; 274985</t>
+          <t>246399; 275448</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>141377; 168752</t>
+          <t>147483; 174670</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290086</t>
+          <t>209662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>290086</t>
+          <t>209662</t>
         </is>
       </c>
     </row>
@@ -2180,42 +2180,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>189573; 227621</t>
+          <t>191340; 230411</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>239894; 279424</t>
+          <t>240460; 278072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>251993; 288918</t>
+          <t>248912; 287176</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>253516; 332305</t>
+          <t>187978; 225514</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>189573; 227621</t>
+          <t>191340; 230411</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>239894; 279424</t>
+          <t>240460; 278072</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>251993; 288918</t>
+          <t>248912; 287176</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>253516; 332305</t>
+          <t>187978; 225514</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>64951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>64951</t>
         </is>
       </c>
     </row>
@@ -2328,42 +2328,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>70992; 99587</t>
+          <t>69741; 98849</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>122445; 150440</t>
+          <t>122592; 150573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81733; 109025</t>
+          <t>80751; 109449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51736; 66797</t>
+          <t>57128; 74032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>70992; 99587</t>
+          <t>69741; 98849</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>122445; 150440</t>
+          <t>122592; 150573</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81733; 109025</t>
+          <t>80751; 109449</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51736; 66797</t>
+          <t>57128; 74032</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
     </row>
@@ -2476,42 +2476,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>111468; 144066</t>
+          <t>110363; 142798</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>134632; 169857</t>
+          <t>136223; 167646</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50459; 78286</t>
+          <t>49515; 76466</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75442; 97405</t>
+          <t>77185; 99909</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>111468; 144066</t>
+          <t>110363; 142798</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>134632; 169857</t>
+          <t>136223; 167646</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50459; 78286</t>
+          <t>49515; 76466</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>75442; 97405</t>
+          <t>77185; 99909</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>337046</t>
+          <t>394812</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>337046</t>
+          <t>394812</t>
         </is>
       </c>
     </row>
@@ -2624,42 +2624,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>380242; 430136</t>
+          <t>377828; 427678</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>413906; 464898</t>
+          <t>413105; 464161</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>393380; 445903</t>
+          <t>394157; 445547</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142939; 496637</t>
+          <t>371274; 412274</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>380242; 430136</t>
+          <t>377828; 427678</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>413906; 464898</t>
+          <t>413105; 464161</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>393380; 445903</t>
+          <t>394157; 445547</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>142939; 496637</t>
+          <t>371274; 412274</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>240870</t>
+          <t>267526</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>240870</t>
+          <t>267526</t>
         </is>
       </c>
     </row>
@@ -2772,42 +2772,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>331445; 388754</t>
+          <t>331796; 386613</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>503596; 559634</t>
+          <t>503359; 560821</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>519558; 573858</t>
+          <t>518203; 572801</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>220180; 260079</t>
+          <t>245719; 290264</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>331445; 388754</t>
+          <t>331796; 386613</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>503596; 559634</t>
+          <t>503359; 560821</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>519558; 573858</t>
+          <t>518203; 572801</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>220180; 260079</t>
+          <t>245719; 290264</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
     </row>
@@ -2920,42 +2920,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2233561; 2345963</t>
+          <t>2233642; 2354668</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2183875; 2297736</t>
+          <t>2178249; 2294711</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1180025; 1722853</t>
+          <t>1564073; 1661715</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2233561; 2345963</t>
+          <t>2233642; 2354668</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2183875; 2297736</t>
+          <t>2178249; 2294711</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1180025; 1722853</t>
+          <t>1564073; 1661715</t>
         </is>
       </c>
     </row>
